--- a/artfynd/A 53633-2024 artfynd.xlsx
+++ b/artfynd/A 53633-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702656</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127705326</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53633-2024 artfynd.xlsx
+++ b/artfynd/A 53633-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702656</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127705326</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53633-2024 artfynd.xlsx
+++ b/artfynd/A 53633-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702656</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127705326</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53633-2024 artfynd.xlsx
+++ b/artfynd/A 53633-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702656</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127705326</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53633-2024 artfynd.xlsx
+++ b/artfynd/A 53633-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702656</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127705326</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53633-2024 artfynd.xlsx
+++ b/artfynd/A 53633-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702656</v>
       </c>
       <c r="B2" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127705326</v>
       </c>
       <c r="B3" t="n">
-        <v>57684</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53633-2024 artfynd.xlsx
+++ b/artfynd/A 53633-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127702656</v>
+        <v>135271899</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>Tosstjänarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495114</v>
+        <v>495014</v>
       </c>
       <c r="R2" t="n">
-        <v>6720481</v>
+        <v>6720344</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,24 +740,29 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bohål i död björk. Bohålet c:a 5 cm stort. 4 meter upp på stammen.</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -773,39 +770,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127705326</v>
+        <v>135274349</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -814,27 +811,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjänarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495140</v>
+        <v>495014</v>
       </c>
       <c r="R3" t="n">
-        <v>6720438</v>
+        <v>6720344</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,27 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohål i Björk.. 5cm i diameter. 6m ovanför marken</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,76 +882,68 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134895876</v>
+        <v>127702656</v>
       </c>
       <c r="B4" t="n">
-        <v>99112</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tosstjänarna, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495014</v>
+        <v>495114</v>
       </c>
       <c r="R4" t="n">
-        <v>6720344</v>
+        <v>6720481</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,36 +967,498 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bohål i död björk. Bohålet c:a 5 cm stort. 4 meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127705326</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>skeberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>495140</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6720438</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bohål i Björk.. 5cm i diameter. 6m ovanför marken</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135273226</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tosstjänarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>495014</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6720344</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Johanna Dalmalm</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Johanna Dalmalm</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135271605</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tosstjänarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>495014</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6720344</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134895876</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tosstjänarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>495014</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6720344</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53633-2024 artfynd.xlsx
+++ b/artfynd/A 53633-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135271899</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274349</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702656</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127705326</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135273226</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,6 +1375,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135271605</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,8 +1494,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134895876</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 53633-2024 artfynd.xlsx
+++ b/artfynd/A 53633-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135271899</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135274349</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135273226</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>135271605</v>
       </c>
       <c r="B7" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53633-2024 artfynd.xlsx
+++ b/artfynd/A 53633-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135271899</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53633-2024 artfynd.xlsx
+++ b/artfynd/A 53633-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,56 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127702656</v>
+        <v>135271899</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tosstjärnarna, Dlr</t>
+          <t>Tosstjänarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495114</v>
+        <v>495014</v>
       </c>
       <c r="R2" t="n">
-        <v>6720481</v>
+        <v>6720344</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,24 +745,29 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bohål i död björk. Bohålet c:a 5 cm stort. 4 meter upp på stammen.</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -778,44 +775,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127702656</t>
+          <t>https://artportalen.se/Sighting/135271899</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127705326</v>
+        <v>135274349</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,27 +821,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>skeberg, Dlr</t>
+          <t>Tosstjänarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495140</v>
+        <v>495014</v>
       </c>
       <c r="R3" t="n">
-        <v>6720438</v>
+        <v>6720344</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,27 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohål i Björk.. 5cm i diameter. 6m ovanför marken</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,81 +892,73 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127705326</t>
+          <t>https://artportalen.se/Sighting/135274349</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134895876</v>
+        <v>127702656</v>
       </c>
       <c r="B4" t="n">
-        <v>99112</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tosstjänarna, Dlr</t>
+          <t>Tosstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495014</v>
+        <v>495114</v>
       </c>
       <c r="R4" t="n">
-        <v>6720344</v>
+        <v>6720481</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,37 +982,519 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bohål i död björk. Bohålet c:a 5 cm stort. 4 meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702656</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127705326</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>skeberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>495140</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6720438</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bohål i Björk.. 5cm i diameter. 6m ovanför marken</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127705326</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135273226</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tosstjänarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>495014</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6720344</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135273226</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135271605</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tosstjänarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>495014</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6720344</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135271605</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134895876</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tosstjänarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>495014</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6720344</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134895876</t>
         </is>
@@ -1042,6 +1505,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
